--- a/output/roomself_excel/4643.xlsx
+++ b/output/roomself_excel/4643.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32248</v>
+        <v>300608</v>
       </c>
       <c r="D2" t="n">
-        <v>1484</v>
+        <v>6160</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>888</v>
       </c>
       <c r="F2" t="n">
-        <v>163</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>300608</v>
+        <v>124740</v>
       </c>
       <c r="D3" t="n">
-        <v>6160</v>
+        <v>2844</v>
       </c>
       <c r="E3" t="n">
-        <v>888</v>
+        <v>315</v>
       </c>
       <c r="F3" t="n">
-        <v>509</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>332489</v>
+        <v>117611</v>
       </c>
       <c r="D4" t="n">
-        <v>6076</v>
+        <v>2816</v>
       </c>
       <c r="E4" t="n">
-        <v>789</v>
+        <v>292</v>
       </c>
       <c r="F4" t="n">
-        <v>512</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14696</v>
+        <v>115381</v>
       </c>
       <c r="D5" t="n">
-        <v>1020</v>
+        <v>2728</v>
       </c>
       <c r="E5" t="n">
-        <v>167</v>
+        <v>371</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22464</v>
+        <v>25702</v>
       </c>
       <c r="D6" t="n">
-        <v>1236</v>
+        <v>1292</v>
       </c>
       <c r="E6" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43407</v>
+        <v>22464</v>
       </c>
       <c r="D7" t="n">
-        <v>1952</v>
+        <v>1236</v>
       </c>
       <c r="E7" t="n">
-        <v>387</v>
+        <v>208</v>
       </c>
       <c r="F7" t="n">
         <v>133</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67893</v>
+        <v>43407</v>
       </c>
       <c r="D8" t="n">
-        <v>2216</v>
+        <v>1952</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29403</v>
+        <v>67893</v>
       </c>
       <c r="D9" t="n">
-        <v>1456</v>
+        <v>2216</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4136</v>
+        <v>54144</v>
       </c>
       <c r="D10" t="n">
-        <v>540</v>
+        <v>1896</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115381</v>
+        <v>22152</v>
       </c>
       <c r="D11" t="n">
-        <v>2728</v>
+        <v>1192</v>
       </c>
       <c r="E11" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83780</v>
+        <v>5439</v>
       </c>
       <c r="D12" t="n">
-        <v>2364</v>
+        <v>640</v>
       </c>
       <c r="E12" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22152</v>
+        <v>32248</v>
       </c>
       <c r="D13" t="n">
-        <v>1192</v>
+        <v>1484</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>107190</v>
+        <v>332489</v>
       </c>
       <c r="D14" t="n">
-        <v>2972</v>
+        <v>6076</v>
       </c>
       <c r="E14" t="n">
-        <v>355</v>
+        <v>789</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4277</v>
+        <v>14696</v>
       </c>
       <c r="D15" t="n">
-        <v>552</v>
+        <v>1020</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -774,14 +774,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25702</v>
+        <v>29403</v>
       </c>
       <c r="D16" t="n">
-        <v>1292</v>
+        <v>1456</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5772</v>
+        <v>4136</v>
       </c>
       <c r="D17" t="n">
-        <v>652</v>
+        <v>540</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5439</v>
+        <v>83780</v>
       </c>
       <c r="D18" t="n">
-        <v>640</v>
+        <v>2364</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3008</v>
+        <v>107190</v>
       </c>
       <c r="D19" t="n">
-        <v>444</v>
+        <v>2972</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>124740</v>
+        <v>4277</v>
       </c>
       <c r="D20" t="n">
-        <v>2844</v>
+        <v>552</v>
       </c>
       <c r="E20" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>127205</v>
+        <v>5772</v>
       </c>
       <c r="D21" t="n">
-        <v>2932</v>
+        <v>652</v>
       </c>
       <c r="E21" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>117611</v>
+        <v>3008</v>
       </c>
       <c r="D22" t="n">
-        <v>2816</v>
+        <v>444</v>
       </c>
       <c r="E22" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>121859</v>
+        <v>127205</v>
       </c>
       <c r="D23" t="n">
-        <v>2844</v>
+        <v>2932</v>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="F23" t="n">
-        <v>211</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>31124</v>
+        <v>121859</v>
       </c>
       <c r="D24" t="n">
-        <v>2088</v>
+        <v>2844</v>
       </c>
       <c r="E24" t="n">
-        <v>230</v>
+        <v>424</v>
       </c>
       <c r="F24" t="n">
-        <v>132</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34727</v>
+        <v>31124</v>
       </c>
       <c r="D25" t="n">
-        <v>2112</v>
+        <v>2088</v>
       </c>
       <c r="E25" t="n">
-        <v>476</v>
+        <v>230</v>
       </c>
       <c r="F25" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>54144</v>
+        <v>34727</v>
       </c>
       <c r="D26" t="n">
-        <v>1896</v>
+        <v>2112</v>
       </c>
       <c r="E26" t="n">
-        <v>314</v>
+        <v>476</v>
       </c>
       <c r="F26" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/4643.xlsx
+++ b/output/roomself_excel/4643.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>6160</v>
       </c>
-      <c r="E2" t="n">
-        <v>888</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>509</v>
+        <v>460</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>472</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>122</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,23 @@
       <c r="D3" t="n">
         <v>2844</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>315</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>25</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>2816</v>
       </c>
-      <c r="E4" t="n">
-        <v>292</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>139</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,23 @@
       <c r="D5" t="n">
         <v>2728</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>371</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>24</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,15 @@
       <c r="D6" t="n">
         <v>1292</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +683,31 @@
       <c r="D7" t="n">
         <v>1236</v>
       </c>
-      <c r="E7" t="n">
-        <v>208</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>133</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>192</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,31 @@
       <c r="D8" t="n">
         <v>1952</v>
       </c>
-      <c r="E8" t="n">
-        <v>387</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>117</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,15 @@
       <c r="D9" t="n">
         <v>2216</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,31 @@
       <c r="D10" t="n">
         <v>1896</v>
       </c>
-      <c r="E10" t="n">
-        <v>314</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>192</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>282</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +831,15 @@
       <c r="D11" t="n">
         <v>1192</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,15 @@
       <c r="D12" t="n">
         <v>640</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +881,31 @@
       <c r="D13" t="n">
         <v>1484</v>
       </c>
-      <c r="E13" t="n">
-        <v>255</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>163</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>139</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +922,38 @@
       <c r="D14" t="n">
         <v>6076</v>
       </c>
-      <c r="E14" t="n">
-        <v>789</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>512</v>
+        <v>719</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>485</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>282</v>
+      </c>
+      <c r="M14" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +971,23 @@
       <c r="D15" t="n">
         <v>1020</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>167</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>27</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1004,15 @@
       <c r="D16" t="n">
         <v>1456</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1029,15 @@
       <c r="D17" t="n">
         <v>540</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1054,23 @@
       <c r="D18" t="n">
         <v>2364</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>355</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>25</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1087,23 @@
       <c r="D19" t="n">
         <v>2972</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>355</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>27</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1120,15 @@
       <c r="D20" t="n">
         <v>552</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1145,15 @@
       <c r="D21" t="n">
         <v>652</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1170,15 @@
       <c r="D22" t="n">
         <v>444</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1195,31 @@
       <c r="D23" t="n">
         <v>2932</v>
       </c>
-      <c r="E23" t="n">
-        <v>437</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>313</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="G23" t="n">
+        <v>27</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>268</v>
+      </c>
+      <c r="J23" t="n">
+        <v>27</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1236,31 @@
       <c r="D24" t="n">
         <v>2844</v>
       </c>
-      <c r="E24" t="n">
-        <v>424</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>211</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="G24" t="n">
+        <v>24</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>187</v>
+      </c>
+      <c r="J24" t="n">
+        <v>24</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1277,31 @@
       <c r="D25" t="n">
         <v>2088</v>
       </c>
-      <c r="E25" t="n">
-        <v>230</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>132</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G25" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>207</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1318,31 @@
       <c r="D26" t="n">
         <v>2112</v>
       </c>
-      <c r="E26" t="n">
-        <v>476</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>104</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>451</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
